--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N8_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.17689666542112</v>
+        <v>7.991245708130932</v>
       </c>
       <c r="D2" t="n">
-        <v>48.94769593877576</v>
+        <v>7.954000590051061</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
